--- a/data/macro/USA/US Unemployment rate.xlsx
+++ b/data/macro/USA/US Unemployment rate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6CB6E7-2F06-4BE3-9CE4-84304C8277E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C3368B-A9B0-4D43-8341-3178654BF83F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
   </bookViews>
@@ -496,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937CB4E7-01E8-4116-8C39-2B0211A5B043}">
-  <dimension ref="A1:H936"/>
+  <dimension ref="A1:H937"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -20334,12 +20334,6 @@
       <c r="A935" s="2">
         <v>45931</v>
       </c>
-      <c r="C935" s="3">
-        <v>0.35416666666666669</v>
-      </c>
-      <c r="D935" s="3" t="s">
-        <v>7</v>
-      </c>
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A936" s="2">
@@ -20362,6 +20356,26 @@
       </c>
       <c r="G936" s="10">
         <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="937" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A937" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B937" s="2">
+        <v>46031</v>
+      </c>
+      <c r="C937" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D937" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F937" s="10">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="G937" s="10">
+        <v>4.5999999999999999E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/US Unemployment rate.xlsx
+++ b/data/macro/USA/US Unemployment rate.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A4280D-6195-44E4-A559-E43CD608FB14}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{521AE3A0-F011-4BC3-82E7-A7D323ED5070}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
   </bookViews>
   <sheets>
     <sheet name="USURTOT" sheetId="1" r:id="rId1"/>
-    <sheet name="info" sheetId="2" r:id="rId2"/>
+    <sheet name="fig" sheetId="3" r:id="rId2"/>
+    <sheet name="info" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="948" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -81,7 +82,7 @@
     <numFmt numFmtId="177" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="178" formatCode="0.0%"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -185,10 +186,10 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -207,6 +208,6465 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>USURTOT!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Actual</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>USURTOT!$B$2:$B$938</c:f>
+              <c:numCache>
+                <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
+                <c:ptCount val="937"/>
+                <c:pt idx="0">
+                  <c:v>17564</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17593</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>17624</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17654</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>17685</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>17715</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>17746</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>17777</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17807</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>17838</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>17868</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>17899</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>17930</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>17958</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>17989</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>18019</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>18050</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18080</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>18111</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>18142</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>18172</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>18203</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>18233</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>18264</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>18295</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>18323</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>18354</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>18384</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>18415</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>18445</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>18476</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>18507</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>18537</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>18568</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>18598</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>18629</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>18660</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>18688</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>18719</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>18749</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>18780</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>18810</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>18841</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>18872</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>18902</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>18933</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>18963</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>18994</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>19025</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>19054</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>19085</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>19115</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>19146</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>19176</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>19207</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>19238</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>19268</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>19299</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>19329</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>19360</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19391</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>19419</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>19450</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19480</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>19511</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>19541</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>19572</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>19603</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>19633</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>19664</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>19694</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>19725</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>19756</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>19784</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>19815</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>19845</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>19876</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>19906</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>19937</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>19968</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>19998</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>20029</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>20059</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20090</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>20121</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>20149</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>20180</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>20210</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>20241</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>20271</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>20302</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>20333</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>20363</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>20394</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>20424</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>20455</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>20486</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>20515</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>20546</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>20576</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>20607</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>20637</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>20668</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>20699</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>20729</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>20760</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>20790</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>20821</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>20852</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>20880</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>20911</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>20941</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>20972</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>21002</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>21033</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>21064</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>21094</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>21125</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>21155</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>21186</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>21217</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>21245</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>21276</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>21306</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>21337</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>21367</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>21398</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>21429</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>21459</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>21490</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>21520</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>21551</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>21591</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>21620</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>21647</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>21681</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>21711</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>21744</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>21774</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>21807</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>21837</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>21866</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>21894</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>21929</c:v>
+                </c:pt>
+                <c:pt idx="144" formatCode="yyyy\-mm\-dd">
+                  <c:v>21962</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>21990</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>22018</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>22047</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>22080</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>22109</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>22138</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>22168</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>22199</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>22230</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>22262</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>22294</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>22321</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>22347</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>22375</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>22403</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>22432</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>22467</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>22495</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>22522</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>22557</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>22588</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>22622</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>22655</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>22677</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>22712</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>22742</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>22775</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>22797</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>22832</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>22859</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>22894</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>22923</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>22950</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>22985</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>23021</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>23042</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>23077</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>23105</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>23133</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>23168</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>23197</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>23224</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>23260</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>23287</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>23315</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>23351</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>23386</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>23413</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>23442</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>23470</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>23504</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>23533</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>23560</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>23595</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>23623</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>23651</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>23686</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>23715</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>23749</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>23776</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>23805</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>23833</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>23868</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>23896</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>23924</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>23959</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>23987</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>24022</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>24050</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>24078</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>24114</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>24146</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>24174</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>24202</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>24233</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>24264</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>24299</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>24327</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>24352</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>24390</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>24415</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>24443</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>24481</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>24512</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>24547</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>24573</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>24601</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>24628</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>24664</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>24692</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>24721</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>24756</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>24783</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>24819</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>24847</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>24875</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>24909</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>24938</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>24966</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>25001</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>25029</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>25057</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>25092</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>25120</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>25148</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>25183</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>25212</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>25245</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>25272</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>25301</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>25328</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>25363</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>25392</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>25419</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>25454</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>25482</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>25514</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>25542</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>25577</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>25605</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>25633</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>25668</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>25696</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>25724</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>25751</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>25787</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>25815</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>25843</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>25878</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>25906</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>25941</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>25969</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>25997</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>26025</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>26060</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>26088</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>26116</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>26151</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>26179</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>26214</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>26242</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>26270</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>26305</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>26333</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>26361</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>26396</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>26424</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>26452</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>26487</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>26515</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>26543</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>26578</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>26606</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>26641</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>26669</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>26697</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>26732</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>26760</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>26788</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>26816</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>26851</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>26879</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>26914</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>26942</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>26970</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>27005</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>27033</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>27061</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>27096</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>27124</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>27152</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>27187</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>27215</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>27243</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>27278</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>27306</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>27334</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>27369</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>27397</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>27432</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>27460</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>27488</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>27516</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>27551</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>27578</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>27607</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>27642</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>27670</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>27705</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>27733</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>27768</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>27796</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>27824</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>27852</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>27887</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>27915</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>27943</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>27978</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>28006</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>28041</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>28069</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>28097</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>28137</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>28160</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>28188</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>28216</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>28251</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>28279</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>28314</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>28342</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>28370</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>28405</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>28433</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>28461</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>28501</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>28524</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>28559</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>28587</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>28615</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>28643</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>28678</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>28706</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>28734</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>28769</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>28797</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>28832</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>28867</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>28888</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>28923</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>28951</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>28979</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>29007</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>29042</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>29070</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>29105</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>29133</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>29161</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>29196</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>29231</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>29252</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>29287</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>29315</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>29343</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>29378</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>29405</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>29434</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>29469</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>29497</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>29532</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>29560</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>29595</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>29623</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>29651</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>29679</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>29714</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>29742</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>29769</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>29805</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>29833</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>29861</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>29896</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>29924</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>29959</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>29987</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>30015</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>30043</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>30078</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>30106</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>30134</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>30169</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>30197</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>30232</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>30260</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>30288</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>30323</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>30351</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>30379</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>30407</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>30442</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>30470</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>30505</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>30533</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>30561</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>30596</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>30624</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>30652</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>30687</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>30715</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>30750</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>30778</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>30806</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>30834</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>30869</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>30897</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>30932</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>30960</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>30988</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>31023</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>31056</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>31079</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>31114</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>31142</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>31170</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>31205</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>31233</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>31261</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>31296</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>31324</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>31352</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>31387</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>31420</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>31450</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>31478</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>31506</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>31534</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>31569</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>31596</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>31625</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>31660</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>31688</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>31723</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>31751</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>31786</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>31814</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>31842</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>31870</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>31905</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>31933</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>31960</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>31996</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>32024</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>32052</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>32087</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>32115</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>32150</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>32178</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>32206</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>32234</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>32269</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>32297</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>32332</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>32360</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>32388</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>32423</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>32451</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>32479</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>32514</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>32542</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>32577</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>32605</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>32633</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>32661</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>32696</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>32724</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>32752</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>32787</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>32815</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>32850</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>32878</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>32906</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>32941</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>32969</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>32997</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>33025</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>33060</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>33088</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>33123</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>33151</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>33179</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>33214</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>33242</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>33270</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>33305</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>33333</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>33361</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>33396</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>33424</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>33452</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>33487</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>33515</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>33543</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>33578</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>33613</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>33641</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>33669</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>33697</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>33732</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>33760</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>33787</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>33823</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>33851</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>33879</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>33914</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>33942</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>33977</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>34005</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>34033</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>34061</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>34096</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>34124</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>34152</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>34187</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>34215</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>34250</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>34278</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>34306</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>34341</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>34369</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>34397</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>34425</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>34460</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>34488</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>34523</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>34551</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>34579</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>34614</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>34642</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>34670</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>34705</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>34733</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>34768</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>34796</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>34824</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>34852</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>34887</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>34915</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>34943</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>34978</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>35006</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>35041</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>35083</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>35097</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>35132</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>35160</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>35188</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>35223</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>35251</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>35279</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>35314</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>35342</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>35370</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>35405</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>35440</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>35468</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>35496</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>35524</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>35552</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>35587</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>35614</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>35643</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>35678</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>35706</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>35741</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>35769</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>35804</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>35832</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>35860</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>35888</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>35923</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>35951</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>35978</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>36014</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>36042</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>36070</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>36104</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>36133</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>36168</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>36196</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>36224</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>36252</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>36287</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>36315</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>36343</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>36378</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>36406</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>36441</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>36469</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>36497</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>36532</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>36560</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>36588</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>36623</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>36651</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>36679</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>36714</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>36742</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>36770</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>36805</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>36833</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>36868</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>36896</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>36924</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>36959</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>36987</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>37015</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>37043</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>37078</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>37106</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>37141</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>37169</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>37197</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>37232</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>37260</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>37288</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>37323</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>37351</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>37379</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>37414</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>37442</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>37470</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>37505</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>37533</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>37561</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>37596</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>37631</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>37659</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>37687</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>37715</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>37743</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>37778</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>37805</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>37834</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>37869</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>37897</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>37932</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>37960</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>37995</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>38023</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>38051</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>38079</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>38114</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>38142</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>38170</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>38205</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>38233</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>38268</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>38296</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>38324</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>38359</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>38387</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>38415</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>38443</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>38478</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>38506</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>38541</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>38569</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>38597</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>38632</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>38660</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>38688</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>38723</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>38751</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>38786</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>38814</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>38842</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>38870</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>38905</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>38933</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>38961</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>38996</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>39024</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>39059</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>39087</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>39115</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>39150</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>39178</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>39206</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>39234</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>39269</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>39297</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>39332</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>39360</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>39388</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>39423</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>39451</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>39479</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>39514</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>39542</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>39570</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>39605</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>39632</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>39661</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>39696</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>39724</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>39759</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>39787</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>39822</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>39850</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>39878</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>39906</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>39941</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>39969</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>39996</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>40032</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>40060</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>40088</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>40123</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>40151</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>40186</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>40214</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>40242</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>40270</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>40305</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>40333</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>40361</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>40396</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>40424</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>40459</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>40487</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>40515</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>40550</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>40578</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>40606</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>40634</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>40669</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>40697</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>40732</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>40760</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>40788</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>40823</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>40851</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>40879</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>40914</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>40942</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>40977</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>41005</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>41033</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>41061</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>41096</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>41124</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>41159</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>41187</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>41215</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>41250</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>41278</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>41306</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>41341</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>41369</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>41397</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>41432</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>41460</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>41488</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>41523</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>41569</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>41586</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>41614</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>41649</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>41677</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>41705</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>41733</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>41761</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>41796</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>41823</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>41852</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>41887</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>41915</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>41950</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>41978</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>42013</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>42041</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>42069</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>42097</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>42132</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>42160</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>42187</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>42223</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>42251</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>42279</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>42314</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>42342</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>42377</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>42405</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>42433</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>42461</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>42496</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>42524</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>42559</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>42587</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>42615</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>42650</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>42678</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>42706</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>42741</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>42769</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>42804</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>42832</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>42860</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>42888</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>42923</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>42951</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>42979</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>43014</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>43042</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>43077</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>43105</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>43133</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>43168</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>43196</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>43224</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>43252</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>43287</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>43315</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>43350</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>43378</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>43406</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>43441</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>43469</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>43497</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>43532</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>43560</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>43588</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>43623</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>43651</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>43679</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>43714</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>43742</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>43770</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>43805</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>43840</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>43868</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>43896</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>43924</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>43959</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>43987</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>44014</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>44050</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>44078</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>44106</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>44141</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>44169</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>44204</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>44232</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>44260</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>44288</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>44323</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>44351</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>44379</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>44414</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>44442</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>44477</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>44505</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>44533</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>44568</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>44596</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>44624</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>44652</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>44687</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>44715</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>44750</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>44778</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>44806</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>44841</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>44869</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>44897</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>44932</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>44960</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>44995</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>45023</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>45051</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>45079</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>45114</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>45142</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>45170</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>45205</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>45233</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>45268</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>45296</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>45324</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>45359</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>45387</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>45415</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>45450</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>45478</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>45506</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>45541</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>45569</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>45597</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>45632</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>45667</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>45695</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>45723</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>45751</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>45779</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>45814</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>45841</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>45870</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>45905</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>45981</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>46007</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>46031</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>46064</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>46087</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>USURTOT!$E$2:$E$938</c:f>
+              <c:numCache>
+                <c:formatCode>0.0%</c:formatCode>
+                <c:ptCount val="937"/>
+                <c:pt idx="0">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.6000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3.7000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.7000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4.4000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5.4000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>6.2000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.7000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>3.6000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3.6000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3.2000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.03</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2.7999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2.8999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2.8999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>3.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>3.6000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5.5999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>5.7999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5.9000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6.2000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>5.7999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5.4000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>4.0999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>4.4000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>4.4000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4.0999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4.4000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5.2000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5.7999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>7.2000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>7.2000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>7.2000000000000008E-2</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>6.2000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5.9000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>5.4000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5.5999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>5.9000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>5.2000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>3.3000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>9.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>0.108</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>0.104</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>0.10299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>0.10100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>0.08</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="500">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="501">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="502">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="503">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="504">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="505">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="506">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="507">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="508">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="509">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="510">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="511">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="512">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="513">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="514">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="515">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="516">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="517">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="518">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="519">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="520">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="521">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="522">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="523">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="524">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="525">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="526">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="527">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="528">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="529">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="530">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="531">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="532">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="533">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="534">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="535">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="536">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="537">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="538">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="539">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="540">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="541">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="542">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="543">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="544">
+                  <c:v>7.0999999999999994E-2</c:v>
+                </c:pt>
+                <c:pt idx="545">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="546">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="547">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="548">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="549">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="550">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="551">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="552">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="553">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="554">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="555">
+                  <c:v>6.4000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="556">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="557">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="558">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="559">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="560">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="561">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="562">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="563">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="564">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="565">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="566">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="567">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="568">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="569">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="570">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="571">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="572">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="573">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="574">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="575">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="576">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="577">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="578">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="579">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="580">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="581">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="582">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="583">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="584">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="585">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="586">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="587">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="588">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="589">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="590">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="591">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="592">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="593">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="594">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="595">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="596">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="597">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="598">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="599">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="600">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="601">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="602">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="603">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="604">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="605">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="606">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="607">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="608">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="609">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="610">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="611">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="612">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="613">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="614">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="615">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="616">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="617">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="618">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="619">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="620">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="621">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="622">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="623">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="624">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="625">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="626">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="627">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="628">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="629">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="630">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="631">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="632">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="633">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="634">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="635">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="636">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="637">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="638">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="639">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="640">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="641">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="642">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="643">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="644">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="645">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="646">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="647">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="648">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="649">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="650">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="651">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="652">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="653">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="654">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="655">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="656">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="657">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="658">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="659">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="660">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="661">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="662">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="663">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="664">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="665">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="666">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="667">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="668">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="669">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="670">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="671">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="672">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="673">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="674">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="675">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="676">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="677">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="678">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="679">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="680">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="681">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="682">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="683">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="684">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="685">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="686">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="687">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="688">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="689">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="690">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="691">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="692">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="693">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="694">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="695">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="696">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="697">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="698">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="699">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="700">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="701">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="702">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="703">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="704">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="705">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="706">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="707">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="708">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="709">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="710">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="711">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="712">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="713">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="714">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="715">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="716">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="717">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="718">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="719">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="720">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="721">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="722">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="723">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="724">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="725">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="726">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="727">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="728">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="729">
+                  <c:v>6.5000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="730">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="731">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="732">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="733">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="734">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="735">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="736">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="737">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="738">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="739">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="740">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="741">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="742">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="743">
+                  <c:v>0.1</c:v>
+                </c:pt>
+                <c:pt idx="744">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="745">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="746">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="747">
+                  <c:v>9.9000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="748">
+                  <c:v>9.7000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="749">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="750">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="751">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="752">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="753">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="754">
+                  <c:v>9.8000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="755">
+                  <c:v>9.4E-2</c:v>
+                </c:pt>
+                <c:pt idx="756">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="757">
+                  <c:v>8.8999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="758">
+                  <c:v>8.7999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="759">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="760">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="761">
+                  <c:v>9.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="762">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="763">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="764">
+                  <c:v>9.0999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="765">
+                  <c:v>0.09</c:v>
+                </c:pt>
+                <c:pt idx="766">
+                  <c:v>8.5999999999999993E-2</c:v>
+                </c:pt>
+                <c:pt idx="767">
+                  <c:v>8.5000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="768">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="769">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="770">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="771">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="772">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="773">
+                  <c:v>8.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="774">
+                  <c:v>8.3000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="775">
+                  <c:v>8.1000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="776">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="777">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="778">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="779">
+                  <c:v>7.8E-2</c:v>
+                </c:pt>
+                <c:pt idx="780">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="781">
+                  <c:v>7.6999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="782">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="783">
+                  <c:v>7.4999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="784">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="785">
+                  <c:v>7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="786">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="787">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="788">
+                  <c:v>7.1999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="789">
+                  <c:v>7.2999999999999995E-2</c:v>
+                </c:pt>
+                <c:pt idx="790">
+                  <c:v>7.0000000000000007E-2</c:v>
+                </c:pt>
+                <c:pt idx="791">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="792">
+                  <c:v>6.6000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="793">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="794">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="795">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="796">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="797">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="798">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="799">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="800">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="801">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="802">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="803">
+                  <c:v>5.6000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="804">
+                  <c:v>5.7000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="805">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="806">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="807">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="808">
+                  <c:v>5.5E-2</c:v>
+                </c:pt>
+                <c:pt idx="809">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="810">
+                  <c:v>5.2999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="811">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="812">
+                  <c:v>5.0999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="813">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="814">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="815">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="816">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="817">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="818">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="819">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="820">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="821">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="822">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="823">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="824">
+                  <c:v>0.05</c:v>
+                </c:pt>
+                <c:pt idx="825">
+                  <c:v>4.9000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="826">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="827">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="828">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="829">
+                  <c:v>4.7E-2</c:v>
+                </c:pt>
+                <c:pt idx="830">
+                  <c:v>4.4999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="831">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="832">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="833">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="834">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="835">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="836">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="837">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="838">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="839">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="840">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="841">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="842">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="843">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="844">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="845">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="846">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="847">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="848">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="849">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="850">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="851">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="852">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="853">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="854">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="855">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="856">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="857">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="858">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="859">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="860">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="861">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="862">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="863">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="864">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="865">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="866">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="867">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="868">
+                  <c:v>0.13300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="869">
+                  <c:v>0.111</c:v>
+                </c:pt>
+                <c:pt idx="870">
+                  <c:v>0.10199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="871">
+                  <c:v>8.4000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="872">
+                  <c:v>7.9000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="873">
+                  <c:v>6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="874">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="875">
+                  <c:v>6.7000000000000004E-2</c:v>
+                </c:pt>
+                <c:pt idx="876">
+                  <c:v>6.3E-2</c:v>
+                </c:pt>
+                <c:pt idx="877">
+                  <c:v>6.2E-2</c:v>
+                </c:pt>
+                <c:pt idx="878">
+                  <c:v>0.06</c:v>
+                </c:pt>
+                <c:pt idx="879">
+                  <c:v>6.0999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="880">
+                  <c:v>5.8000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="881">
+                  <c:v>5.8999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="882">
+                  <c:v>5.3999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="883">
+                  <c:v>5.1999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="884">
+                  <c:v>4.8000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="885">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="886">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="887">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="888">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="889">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="890">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="891">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="892">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="893">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="894">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="895">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="896">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="897">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="898">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="899">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="900">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="901">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="902">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="903">
+                  <c:v>3.4000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="904">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="905">
+                  <c:v>3.5999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="906">
+                  <c:v>3.5000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="907">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="908">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="909">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="910">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="911">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="912">
+                  <c:v>3.6999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="913">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="914">
+                  <c:v>3.7999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="915">
+                  <c:v>3.9E-2</c:v>
+                </c:pt>
+                <c:pt idx="916">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="917">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="918">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="919">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="920">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="921">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="922">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="923">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="924">
+                  <c:v>0.04</c:v>
+                </c:pt>
+                <c:pt idx="925">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="926">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="927">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="928">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="929">
+                  <c:v>4.1000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="930">
+                  <c:v>4.2000000000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="931">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="932">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="933">
+                  <c:v>4.5999999999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="934">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="935">
+                  <c:v>4.2999999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="936">
+                  <c:v>4.3999999999999997E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DE0D-48B7-9E1E-EC148CED7ED4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1737611759"/>
+        <c:axId val="1229854863"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1737611759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="yyyy;@" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1229854863"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="days"/>
+        <c:majorUnit val="5"/>
+        <c:majorTimeUnit val="years"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="1229854863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1737611759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609599</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="차트 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{48F91784-7AE2-4105-8E55-68E4FF136FDB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,7 +6966,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937CB4E7-01E8-4116-8C39-2B0211A5B043}">
-  <dimension ref="A1:H937"/>
+  <dimension ref="A1:H938"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" style="7" bestFit="1" customWidth="1"/>
@@ -20410,6 +26870,29 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
+    <row r="938" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A938" s="7">
+        <v>46054</v>
+      </c>
+      <c r="B938" s="7">
+        <v>46087</v>
+      </c>
+      <c r="C938" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D938" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E938" s="9">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="F938" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G938" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20418,6 +26901,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63624C48-49F6-45B9-A627-4576E9CBFBE4}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA19B7F8-4183-46E9-B189-03FA54B61813}">
   <dimension ref="B2:C3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>

--- a/data/macro/USA/US Unemployment rate.xlsx
+++ b/data/macro/USA/US Unemployment rate.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E330717-4DF3-45FB-A48A-1DDC9D06BD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A700D7E3-1F9C-44BA-8647-97F7572D7253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3015C15E-E65F-49A3-B944-3369C7E9EBA4}"/>
   </bookViews>
   <sheets>
     <sheet name="USURTOT" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="13">
   <si>
     <t>Release Date</t>
   </si>
@@ -6982,7 +6982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937CB4E7-01E8-4116-8C39-2B0211A5B043}">
-  <dimension ref="A1:H939"/>
+  <dimension ref="A1:H940"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.44140625" style="7" bestFit="1" customWidth="1"/>
@@ -7016,7 +7016,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>17533</v>
       </c>
@@ -7033,7 +7033,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>17564</v>
       </c>
@@ -7053,7 +7053,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>17593</v>
       </c>
@@ -7073,7 +7073,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>17624</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>17654</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>17685</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>17715</v>
       </c>
@@ -7153,7 +7153,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>17746</v>
       </c>
@@ -7173,7 +7173,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="6">
         <v>17777</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="6">
         <v>17807</v>
       </c>
@@ -7213,7 +7213,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="6">
         <v>17838</v>
       </c>
@@ -7233,7 +7233,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="6">
         <v>17868</v>
       </c>
@@ -7253,7 +7253,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>17899</v>
       </c>
@@ -7273,7 +7273,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>17930</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>17958</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>17989</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>18019</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>18050</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>18080</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="6">
         <v>18111</v>
       </c>
@@ -7413,7 +7413,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>18142</v>
       </c>
@@ -7433,7 +7433,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>18172</v>
       </c>
@@ -7453,7 +7453,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>18203</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>18233</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>18264</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>18295</v>
       </c>
@@ -7533,7 +7533,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>18323</v>
       </c>
@@ -7553,7 +7553,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>18354</v>
       </c>
@@ -7573,7 +7573,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
         <v>18384</v>
       </c>
@@ -7593,7 +7593,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
         <v>18415</v>
       </c>
@@ -7613,7 +7613,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
         <v>18445</v>
       </c>
@@ -7633,7 +7633,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="6">
         <v>18476</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="6">
         <v>18507</v>
       </c>
@@ -7673,7 +7673,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
         <v>18537</v>
       </c>
@@ -7693,7 +7693,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="6">
         <v>18568</v>
       </c>
@@ -7713,7 +7713,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>18598</v>
       </c>
@@ -7733,7 +7733,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>18629</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>18660</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>3.7000000000000005E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>18688</v>
       </c>
@@ -7793,7 +7793,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>18719</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>18749</v>
       </c>
@@ -7833,7 +7833,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>18780</v>
       </c>
@@ -7853,7 +7853,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="6">
         <v>18810</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>18841</v>
       </c>
@@ -7893,7 +7893,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>18872</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>18902</v>
       </c>
@@ -7933,7 +7933,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>18933</v>
       </c>
@@ -7953,7 +7953,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>18963</v>
       </c>
@@ -7973,7 +7973,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>18994</v>
       </c>
@@ -7993,7 +7993,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>19025</v>
       </c>
@@ -8013,7 +8013,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>19054</v>
       </c>
@@ -8033,7 +8033,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="6">
         <v>19085</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>19115</v>
       </c>
@@ -8073,7 +8073,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>19146</v>
       </c>
@@ -8093,7 +8093,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>19176</v>
       </c>
@@ -8113,7 +8113,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>19207</v>
       </c>
@@ -8133,7 +8133,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>19238</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>19268</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>19299</v>
       </c>
@@ -8193,7 +8193,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>19329</v>
       </c>
@@ -8213,7 +8213,7 @@
         <v>2.7999999999999997E-2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="6">
         <v>19360</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>19391</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>2.8999999999999998E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>19419</v>
       </c>
@@ -8273,7 +8273,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>19450</v>
       </c>
@@ -8293,7 +8293,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>19480</v>
       </c>
@@ -8313,7 +8313,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>19511</v>
       </c>
@@ -8333,7 +8333,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>19541</v>
       </c>
@@ -8353,7 +8353,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="6">
         <v>19572</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>2.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="6">
         <v>19603</v>
       </c>
@@ -8393,7 +8393,7 @@
         <v>2.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>19633</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>2.8999999999999998E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>19664</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>3.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>19694</v>
       </c>
@@ -8453,7 +8453,7 @@
         <v>3.6000000000000004E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>19725</v>
       </c>
@@ -8473,7 +8473,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>19756</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>19784</v>
       </c>
@@ -8513,7 +8513,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>19815</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="6">
         <v>19845</v>
       </c>
@@ -8553,7 +8553,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>19876</v>
       </c>
@@ -8573,7 +8573,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>19906</v>
       </c>
@@ -8593,7 +8593,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>19937</v>
       </c>
@@ -8613,7 +8613,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>19968</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>19998</v>
       </c>
@@ -8653,7 +8653,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>20029</v>
       </c>
@@ -8673,7 +8673,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="6">
         <v>20059</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="6">
         <v>20090</v>
       </c>
@@ -8713,7 +8713,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>20121</v>
       </c>
@@ -8733,7 +8733,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>20149</v>
       </c>
@@ -8753,7 +8753,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>20180</v>
       </c>
@@ -8773,7 +8773,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>20210</v>
       </c>
@@ -8793,7 +8793,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>20241</v>
       </c>
@@ -8813,7 +8813,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>20271</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>20302</v>
       </c>
@@ -8853,7 +8853,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="6">
         <v>20333</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>20363</v>
       </c>
@@ -8893,7 +8893,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>20394</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>20424</v>
       </c>
@@ -8933,7 +8933,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>20455</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>20486</v>
       </c>
@@ -8973,7 +8973,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>20515</v>
       </c>
@@ -8993,7 +8993,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="6">
         <v>20546</v>
       </c>
@@ -9013,7 +9013,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="6">
         <v>20576</v>
       </c>
@@ -9033,7 +9033,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>20607</v>
       </c>
@@ -9053,7 +9053,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>20637</v>
       </c>
@@ -9073,7 +9073,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>20668</v>
       </c>
@@ -9093,7 +9093,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>20699</v>
       </c>
@@ -9113,7 +9113,7 @@
         <v>4.0999999999999995E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>20729</v>
       </c>
@@ -9133,7 +9133,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>20760</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>20790</v>
       </c>
@@ -9173,7 +9173,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="6">
         <v>20821</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>20852</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>20880</v>
       </c>
@@ -9233,7 +9233,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>20911</v>
       </c>
@@ -9253,7 +9253,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>20941</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>20972</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>21002</v>
       </c>
@@ -9313,7 +9313,7 @@
         <v>4.4000000000000004E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="6">
         <v>21033</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="6">
         <v>21064</v>
       </c>
@@ -9353,7 +9353,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>21094</v>
       </c>
@@ -9373,7 +9373,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>21125</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>21155</v>
       </c>
@@ -9413,7 +9413,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>21186</v>
       </c>
@@ -9433,7 +9433,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>21217</v>
       </c>
@@ -9453,7 +9453,7 @@
         <v>5.7999999999999996E-2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>21245</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>21276</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>21306</v>
       </c>
@@ -9513,7 +9513,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="6">
         <v>21337</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="6">
         <v>21367</v>
       </c>
@@ -9553,7 +9553,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="6">
         <v>21398</v>
       </c>
@@ -9573,7 +9573,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="6">
         <v>21429</v>
       </c>
@@ -9593,7 +9593,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="6">
         <v>21459</v>
       </c>
@@ -9613,7 +9613,7 @@
         <v>7.2000000000000008E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="6">
         <v>21490</v>
       </c>
@@ -9633,7 +9633,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="6">
         <v>21520</v>
       </c>
@@ -9653,7 +9653,7 @@
         <v>6.2000000000000006E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="6">
         <v>21551</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="6">
         <v>21582</v>
       </c>
@@ -9693,7 +9693,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="6">
         <v>21610</v>
       </c>
@@ -9713,7 +9713,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="6">
         <v>21641</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="6">
         <v>21671</v>
       </c>
@@ -9753,7 +9753,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="6">
         <v>21702</v>
       </c>
@@ -9773,7 +9773,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="6">
         <v>21732</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="6">
         <v>21763</v>
       </c>
@@ -9813,7 +9813,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="6">
         <v>21794</v>
       </c>
@@ -9833,7 +9833,7 @@
         <v>5.4000000000000006E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="6">
         <v>21824</v>
       </c>
@@ -9853,7 +9853,7 @@
         <v>5.5999999999999994E-2</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="6">
         <v>21855</v>
       </c>
@@ -9873,7 +9873,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="6">
         <v>21885</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>5.9000000000000004E-2</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="6">
         <v>21916</v>
       </c>
@@ -9913,7 +9913,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="6">
         <v>21947</v>
       </c>
@@ -9933,7 +9933,7 @@
         <v>5.2000000000000005E-2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="6">
         <v>21976</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="6">
         <v>22007</v>
       </c>
@@ -9973,7 +9973,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="6">
         <v>22037</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="6">
         <v>22068</v>
       </c>
@@ -10013,7 +10013,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="6">
         <v>22098</v>
       </c>
@@ -10033,7 +10033,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="6">
         <v>22129</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="6">
         <v>22160</v>
       </c>
@@ -10073,7 +10073,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="6">
         <v>22190</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="156" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="6">
         <v>22221</v>
       </c>
@@ -10113,7 +10113,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="157" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="6">
         <v>22251</v>
       </c>
@@ -10133,7 +10133,7 @@
         <v>6.3E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="6">
         <v>22282</v>
       </c>
@@ -10153,7 +10153,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="159" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="6">
         <v>22313</v>
       </c>
@@ -10173,7 +10173,7 @@
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="6">
         <v>22341</v>
       </c>
@@ -10193,7 +10193,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="6">
         <v>22372</v>
       </c>
@@ -10213,7 +10213,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="6">
         <v>22402</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="163" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="6">
         <v>22433</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="6">
         <v>22463</v>
       </c>
@@ -10273,7 +10273,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="6">
         <v>22494</v>
       </c>
@@ -10293,7 +10293,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="6">
         <v>22525</v>
       </c>
@@ -10313,7 +10313,7 @@
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
-    <row r="167" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="6">
         <v>22555</v>
       </c>
@@ -10333,7 +10333,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="168" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="6">
         <v>22586</v>
       </c>
@@ -10353,7 +10353,7 @@
         <v>6.8000000000000005E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="6">
         <v>22616</v>
       </c>
@@ -10373,7 +10373,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="6">
         <v>22647</v>
       </c>
@@ -10393,7 +10393,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="6">
         <v>22678</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="6">
         <v>22706</v>
       </c>
@@ -10433,7 +10433,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="6">
         <v>22737</v>
       </c>
@@ -10453,7 +10453,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="6">
         <v>22767</v>
       </c>
@@ -10473,7 +10473,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="6">
         <v>22798</v>
       </c>
@@ -10493,7 +10493,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="6">
         <v>22828</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="6">
         <v>22859</v>
       </c>
@@ -10533,7 +10533,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="6">
         <v>22890</v>
       </c>
@@ -10553,7 +10553,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="6">
         <v>22920</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="6">
         <v>22951</v>
       </c>
@@ -10593,7 +10593,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="6">
         <v>22981</v>
       </c>
@@ -10613,7 +10613,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="6">
         <v>23012</v>
       </c>
@@ -10633,7 +10633,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="6">
         <v>23043</v>
       </c>
@@ -10653,7 +10653,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="6">
         <v>23071</v>
       </c>
@@ -10673,7 +10673,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="6">
         <v>23102</v>
       </c>
@@ -10693,7 +10693,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="6">
         <v>23132</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="6">
         <v>23163</v>
       </c>
@@ -10733,7 +10733,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="6">
         <v>23193</v>
       </c>
@@ -10753,7 +10753,7 @@
         <v>5.7000000000000002E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="6">
         <v>23224</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="6">
         <v>23255</v>
       </c>
@@ -10793,7 +10793,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="6">
         <v>23285</v>
       </c>
@@ -10813,7 +10813,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="6">
         <v>23316</v>
       </c>
@@ -10833,7 +10833,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="6">
         <v>23346</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="194" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="6">
         <v>23377</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="6">
         <v>23408</v>
       </c>
@@ -10893,7 +10893,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="196" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="6">
         <v>23437</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="6">
         <v>23468</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="6">
         <v>23498</v>
       </c>
@@ -10953,7 +10953,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="6">
         <v>23529</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="6">
         <v>23559</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="6">
         <v>23590</v>
       </c>
@@ -11013,7 +11013,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="202" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="6">
         <v>23621</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="6">
         <v>23651</v>
       </c>
@@ -11053,7 +11053,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="6">
         <v>23682</v>
       </c>
@@ -11073,7 +11073,7 @@
         <v>5.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="6">
         <v>23712</v>
       </c>
@@ -11093,7 +11093,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="206" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="6">
         <v>23743</v>
       </c>
@@ -11113,7 +11113,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="207" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="6">
         <v>23774</v>
       </c>
@@ -11133,7 +11133,7 @@
         <v>4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="6">
         <v>23802</v>
       </c>
@@ -11153,7 +11153,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="6">
         <v>23833</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="6">
         <v>23863</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="6">
         <v>23894</v>
       </c>
@@ -11213,7 +11213,7 @@
         <v>4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="6">
         <v>23924</v>
       </c>
@@ -11233,7 +11233,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="6">
         <v>23955</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="214" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="6">
         <v>23986</v>
       </c>
@@ -11273,7 +11273,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="215" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="6">
         <v>24016</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="216" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="6">
         <v>24047</v>
       </c>
@@ -11313,7 +11313,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="6">
         <v>24077</v>
       </c>
@@ -11333,7 +11333,7 @@
         <v>4.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="6">
         <v>24108</v>
       </c>
@@ -11353,7 +11353,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="219" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="6">
         <v>24139</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="220" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="6">
         <v>24167</v>
       </c>
@@ -11393,7 +11393,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="221" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="6">
         <v>24198</v>
       </c>
@@ -11413,7 +11413,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="6">
         <v>24228</v>
       </c>
@@ -11433,7 +11433,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="6">
         <v>24259</v>
       </c>
@@ -11453,7 +11453,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="224" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="6">
         <v>24289</v>
       </c>
@@ -11473,7 +11473,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="6">
         <v>24320</v>
       </c>
@@ -11493,7 +11493,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="6">
         <v>24351</v>
       </c>
@@ -11513,7 +11513,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="227" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="6">
         <v>24381</v>
       </c>
@@ -11533,7 +11533,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="6">
         <v>24412</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="6">
         <v>24442</v>
       </c>
@@ -11573,7 +11573,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="6">
         <v>24473</v>
       </c>
@@ -11593,7 +11593,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="6">
         <v>24504</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="6">
         <v>24532</v>
       </c>
@@ -11633,7 +11633,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="6">
         <v>24563</v>
       </c>
@@ -11653,7 +11653,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="6">
         <v>24593</v>
       </c>
@@ -11673,7 +11673,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="6">
         <v>24624</v>
       </c>
@@ -11693,7 +11693,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="6">
         <v>24654</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="237" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="6">
         <v>24685</v>
       </c>
@@ -11733,7 +11733,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="238" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="6">
         <v>24716</v>
       </c>
@@ -11753,7 +11753,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="6">
         <v>24746</v>
       </c>
@@ -11773,7 +11773,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="6">
         <v>24777</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="6">
         <v>24807</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>3.9E-2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="6">
         <v>24838</v>
       </c>
@@ -11833,7 +11833,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="6">
         <v>24869</v>
       </c>
@@ -11853,7 +11853,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="6">
         <v>24898</v>
       </c>
@@ -11873,7 +11873,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="6">
         <v>24929</v>
       </c>
@@ -11893,7 +11893,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="6">
         <v>24959</v>
       </c>
@@ -11913,7 +11913,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="6">
         <v>24990</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="6">
         <v>25020</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="6">
         <v>25051</v>
       </c>
@@ -11973,7 +11973,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="6">
         <v>25082</v>
       </c>
@@ -11993,7 +11993,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="251" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="6">
         <v>25112</v>
       </c>
@@ -12013,7 +12013,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="252" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="6">
         <v>25143</v>
       </c>
@@ -12033,7 +12033,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="253" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="6">
         <v>25173</v>
       </c>
@@ -12053,7 +12053,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="6">
         <v>25204</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="255" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="6">
         <v>25235</v>
       </c>
@@ -12093,7 +12093,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="6">
         <v>25263</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="6">
         <v>25294</v>
       </c>
@@ -12133,7 +12133,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="258" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="6">
         <v>25324</v>
       </c>
@@ -12153,7 +12153,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="6">
         <v>25355</v>
       </c>
@@ -12173,7 +12173,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="6">
         <v>25385</v>
       </c>
@@ -12193,7 +12193,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="6">
         <v>25416</v>
       </c>
@@ -12213,7 +12213,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="6">
         <v>25447</v>
       </c>
@@ -12233,7 +12233,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="6">
         <v>25477</v>
       </c>
@@ -12253,7 +12253,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="264" spans="1:8" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="6">
         <v>25508</v>
       </c>
@@ -26930,6 +26930,26 @@
       </c>
       <c r="G939" s="9">
         <v>4.3999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="940" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A940" s="7">
+        <v>46113</v>
+      </c>
+      <c r="B940" s="7">
+        <v>46150</v>
+      </c>
+      <c r="C940" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="D940" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F940" s="9">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="G940" s="9">
+        <v>4.2999999999999997E-2</v>
       </c>
     </row>
   </sheetData>
